--- a/diseases/d042/2005-2009.xlsx
+++ b/diseases/d042/2005-2009.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6930,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -12657,9 +12651,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18372,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -24103,9 +24091,6 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
